--- a/docs/coursework/review-2026-10-01/FixProof-15-candidate-test-evidence.xlsx
+++ b/docs/coursework/review-2026-10-01/FixProof-15-candidate-test-evidence.xlsx
@@ -251,7 +251,7 @@
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-01T11:55:31.796037Z</t>
+          <t xml:space="preserve">2026-10-22T03:42:34.841345Z</t>
         </is>
       </c>
     </row>
